--- a/output/2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Filiale diretta del gruppo Safetyware (produttore e distributore di PPE/sicurezza industriale), Kuching (City Square Phase II, Jalan Pending); indirizzo e telefono confermati su safetyware.com/our-locations. Settore principale PPE/sicurezza industriale, non utensileria in senso stretto: verificare pertinenza. Essendo filiale propria del produttore e non un distributore terzo indipendente, valutare se rientra nel target "distributore partner".</t>
+          <t>Filiale diretta del gruppo Safetyware (produttore e distributore di PPE/sicurezza industriale), Kuching (City Square Phase II, Jalan Pending); indirizzo e telefono confermati su safetyware.com/our-locations. Settore principale PPE/sicurezza industriale, non utensileria in senso stretto: verificare pertinenza. Essendo filiale propria del produttore e non un distributore terzo indipendente, valutare se rientra nel target "distributore partner". [DUPLICATO — vedi anche: 2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Marketplace/distributore B2B consolidato di fasteners, utensili manuali ed elettrici, consumabili, abrasivi e dust extractors. Sede legale a Klang, Selangor: nessuna sede fisica in Sarawak, ma pagine ufficiali dedicate su lapasar.com (mro-industrial-supplies-supplier-kuching e -miri) confermano servizio attivo e logistica consolidata verso Kuching e Miri. Telefono ed email riportati nella lista grezza non confermati autonomamente da fonte indipendente: verificare umanamente.</t>
+          <t>Marketplace/distributore B2B consolidato di fasteners, utensili manuali ed elettrici, consumabili, abrasivi e dust extractors. Sede legale a Klang, Selangor: nessuna sede fisica in Sarawak, ma pagine ufficiali dedicate su lapasar.com (mro-industrial-supplies-supplier-kuching e -miri) confermano servizio attivo e logistica consolidata verso Kuching e Miri. Telefono ed email riportati nella lista grezza non confermati autonomamente da fonte indipendente: verificare umanamente. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Rivenditore hardware industriale e power tools multi-brand (Makita, Worx, Hikoki), Kuching. Verificato su magicpin.com (indirizzo e telefono coincidenti, recensioni attive, rating 4.4/5). Sito ufficiale non reperito.</t>
+          <t>Rivenditore hardware industriale e power tools multi-brand (Makita, Worx, Hikoki), Kuching. Verificato su magicpin.com (indirizzo e telefono coincidenti, recensioni attive, rating 4.4/5). Sito ufficiale non reperito. [DUPLICATO — vedi anche: 2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Dealer autorizzato SANY (macchinari pesanti, equipaggiamento e componenti) per Sarawak e Sabah, costituita nel 2018; sede a Bintulu con filiali a Kuching, Miri e Sibu (copertura capillare). Verificato su my.hiredly.com (company page). Sito ufficiale e telefono non reperiti in ricerca.</t>
+          <t>Dealer autorizzato SANY (macchinari pesanti, equipaggiamento e componenti) per Sarawak e Sabah, costituita nel 2018; sede a Bintulu con filiali a Kuching, Miri e Sibu (copertura capillare). Verificato su my.hiredly.com (company page). Sito ufficiale e telefono non reperiti in ricerca. [DUPLICATO — vedi anche: 2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Distributore di cuscinetti (bearings) e componenti meccanici industriali, Kuching (Central World, Jalan Merbau off Jalan Pending). Contatti confermati su noonsite.com, coerenti con il dominio del gruppo SLS Bearings (slsbearings.com).</t>
+          <t>Distributore di cuscinetti (bearings) e componenti meccanici industriali, Kuching (Central World, Jalan Merbau off Jalan Pending). Contatti confermati su noonsite.com, coerenti con il dominio del gruppo SLS Bearings (slsbearings.com). [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Wholesaler di macchinari industriali, equipaggiamento e materiali edili, Sibu (Khoo Peng Loong Road); costituita nel 1990. Verificato su emis.com (indirizzo e dati societari coincidenti).</t>
+          <t>Wholesaler di macchinari industriali, equipaggiamento e materiali edili, Sibu (Khoo Peng Loong Road); costituita nel 1990. Verificato su emis.com (indirizzo e dati societari coincidenti). [DUPLICATO — vedi anche: 2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Trading B2B di ricambi per macchinari movimento terra (Caterpillar, Komatsu, Hitachi, Kobelco), Miri (Piasau Business Park); oltre 30 anni di attivita'. Verificato su sgpgrid.com (indirizzo coincidente). Sito ufficiale e telefono non reperiti in ricerca.</t>
+          <t>Trading B2B di ricambi per macchinari movimento terra (Caterpillar, Komatsu, Hitachi, Kobelco), Miri (Piasau Business Park); oltre 30 anni di attivita'. Verificato su sgpgrid.com (indirizzo coincidente). Sito ufficiale e telefono non reperiti in ricerca. [DUPLICATO — vedi anche: 2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
